--- a/tables/Datas/task.xlsx
+++ b/tables/Datas/task.xlsx
@@ -85,7 +85,7 @@
     <t>next_id</t>
   </si>
   <si>
-    <t>params</t>
+    <t>task_params</t>
   </si>
   <si>
     <t>goal</t>
